--- a/course-design-2/outputs/tables/ch8/38_stage26_1_F_group_leakage_ablation.xlsx
+++ b/course-design-2/outputs/tables/ch8/38_stage26_1_F_group_leakage_ablation.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>缺失数（14,883 建模样本口径）</t>
+          <t>缺失数（14,883 建模样本统计范围）</t>
         </is>
       </c>
     </row>
